--- a/r5-TC-FHIR-AG-Scheduling-R5-133-56---resolve-todo-for-example-search-urls/StructureDefinition-virtual-service-detail.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-133-56---resolve-todo-for-example-search-urls/StructureDefinition-virtual-service-detail.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/virtual-service-detail</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/virtual-service-detail</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:33:33+00:00</t>
+    <t>2026-08-18T09:10:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
